--- a/plc/s7-1x00/core/system/system-v3.0.xlsx
+++ b/plc/s7-1x00/core/system/system-v3.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\PlcFramework\code\plc\s7-1x00\core\system\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D102D76-72DD-4393-863D-311D844A393A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28E63894-CBC1-4828-A3A8-C201B0855FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="18570" yWindow="-16365" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="PLC Tags" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="355" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="360" uniqueCount="127">
   <si>
     <t>Name</t>
   </si>
@@ -396,16 +396,27 @@
   </si>
   <si>
     <t>Provisional true</t>
+  </si>
+  <si>
+    <t>system</t>
+  </si>
+  <si>
+    <t>{"version":"v3.0","author":"cyanezf","family":"core/system","status":"current","deprecatedBy":null,"dependencies":[]}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -428,8 +439,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -745,7 +757,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J34"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="16.6328125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.90625" bestFit="1" customWidth="1"/>
@@ -759,7 +771,7 @@
     <col min="10" max="10" width="9.36328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -791,7 +803,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -823,7 +835,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -855,7 +867,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:10">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -887,7 +899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -919,7 +931,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>28</v>
       </c>
@@ -951,7 +963,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>31</v>
       </c>
@@ -983,7 +995,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>34</v>
       </c>
@@ -1015,7 +1027,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>37</v>
       </c>
@@ -1047,7 +1059,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1079,7 +1091,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>43</v>
       </c>
@@ -1111,7 +1123,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>46</v>
       </c>
@@ -1143,7 +1155,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>49</v>
       </c>
@@ -1175,7 +1187,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -1207,7 +1219,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>55</v>
       </c>
@@ -1239,7 +1251,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>58</v>
       </c>
@@ -1271,7 +1283,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="17" spans="1:10">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>61</v>
       </c>
@@ -1303,7 +1315,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:10">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>64</v>
       </c>
@@ -1335,7 +1347,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:10">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>67</v>
       </c>
@@ -1367,7 +1379,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:10">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>70</v>
       </c>
@@ -1399,7 +1411,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:10">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>73</v>
       </c>
@@ -1431,7 +1443,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="1:10">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>76</v>
       </c>
@@ -1463,7 +1475,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" spans="1:10">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>79</v>
       </c>
@@ -1495,7 +1507,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="24" spans="1:10">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>82</v>
       </c>
@@ -1527,7 +1539,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="25" spans="1:10">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>85</v>
       </c>
@@ -1559,7 +1571,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="26" spans="1:10">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>88</v>
       </c>
@@ -1591,7 +1603,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="27" spans="1:10">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>92</v>
       </c>
@@ -1623,7 +1635,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="28" spans="1:10">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>95</v>
       </c>
@@ -1655,7 +1667,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="29" spans="1:10">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>98</v>
       </c>
@@ -1687,7 +1699,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>101</v>
       </c>
@@ -1719,7 +1731,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>104</v>
       </c>
@@ -1751,7 +1763,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>107</v>
       </c>
@@ -1783,7 +1795,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="33" spans="1:10">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>111</v>
       </c>
@@ -1815,7 +1827,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="34" spans="1:10">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>114</v>
       </c>
@@ -1854,10 +1866,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1874,41 +1886,59 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>119</v>
       </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C2" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" t="s">
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" t="s">
         <v>120</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E3" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" t="s">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>122</v>
       </c>
-      <c r="B3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4" t="s">
         <v>123</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E4" t="s">
         <v>124</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>